--- a/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
+++ b/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Financial Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E67DC5-167A-47BA-9D49-9438F1D52614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E6C36D-9E7E-4DBF-B204-9F75B7C77256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
   <si>
     <t>Prinicipal Amount</t>
   </si>
@@ -79,19 +79,13 @@
     <t>FINACIAL FUNCTIONS</t>
   </si>
   <si>
-    <t>FV(C10,D10,B10)</t>
-  </si>
-  <si>
-    <t>PMT(C13/12,D13*12,B12)</t>
-  </si>
-  <si>
-    <t>PPMT(C16/12,1,D16*12,B16)</t>
-  </si>
-  <si>
-    <t>IPMT(C19/12,1,D19*12,B19)</t>
-  </si>
-  <si>
-    <t>FV(C22,D22,,B22)</t>
+    <t>PV - Present Value</t>
+  </si>
+  <si>
+    <t>PMT - Per Month Amount</t>
+  </si>
+  <si>
+    <t>FV - Future Value</t>
   </si>
 </sst>
 </file>
@@ -330,7 +324,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>440726</xdr:colOff>
+      <xdr:colOff>447076</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>56105</xdr:rowOff>
     </xdr:to>
@@ -674,6 +668,7 @@
   <dimension ref="A4:AD34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="8.6328125" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
@@ -714,6 +709,9 @@
       <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="10" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="4">
@@ -725,16 +723,10 @@
       <c r="D10" s="6">
         <v>5</v>
       </c>
-      <c r="E10" s="7">
-        <f>FV(C10,D10,,B10)</f>
-        <v>100010.55706850003</v>
-      </c>
-      <c r="F10" s="8" t="str">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8" t="e">
         <f ca="1">_xlfn.FORMULATEXT(E10)</f>
-        <v>=FV(C10,D10,,B10)</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
+        <v>#N/A</v>
       </c>
       <c r="H10" s="9"/>
       <c r="J10" s="10"/>
@@ -769,6 +761,9 @@
       <c r="C11" s="12"/>
       <c r="E11" s="13"/>
       <c r="F11" s="8"/>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" s="22">
@@ -798,13 +793,10 @@
       <c r="D13" s="6">
         <v>3</v>
       </c>
-      <c r="E13" s="7">
-        <f>PMT(C13/12,D13*12,B13)</f>
-        <v>-2051.8899325312309</v>
-      </c>
-      <c r="F13" t="str">
+      <c r="E13" s="7"/>
+      <c r="F13" t="e">
         <f ca="1">_xlfn.FORMULATEXT(E13)</f>
-        <v>=PMT(C13/12,D13*12,B13)</v>
+        <v>#N/A</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -842,16 +834,10 @@
       <c r="D16" s="6">
         <v>3</v>
       </c>
-      <c r="E16" s="7">
-        <f>PPMT(C16/12,1,D16*12,B16)</f>
-        <v>-1591.4732658645644</v>
-      </c>
-      <c r="F16" t="str">
+      <c r="E16" s="7"/>
+      <c r="F16" t="e">
         <f ca="1">_xlfn.FORMULATEXT(E16)</f>
-        <v>=PPMT(C16/12,1,D16*12,B16)</v>
-      </c>
-      <c r="G16" t="s">
-        <v>16</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -886,16 +872,10 @@
       <c r="D19" s="6">
         <v>3</v>
       </c>
-      <c r="E19" s="7">
-        <f>IPMT(C19/12,1,D19*12,B19)</f>
-        <v>-460.41666666666674</v>
-      </c>
-      <c r="F19" t="str">
+      <c r="E19" s="7"/>
+      <c r="F19" t="e">
         <f ca="1">_xlfn.FORMULATEXT(E19)</f>
-        <v>=IPMT(C19/12,1,D19*12,B19)</v>
-      </c>
-      <c r="G19" t="s">
-        <v>17</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -930,16 +910,10 @@
       <c r="D22" s="6">
         <v>5</v>
       </c>
-      <c r="E22" s="7">
-        <f>FV(C22,D22,,B22)</f>
-        <v>37160.327581525875</v>
-      </c>
-      <c r="F22" t="str">
+      <c r="E22" s="7"/>
+      <c r="F22" t="e">
         <f ca="1">_xlfn.FORMULATEXT(E22)</f>
-        <v>=FV(C22,D22,,B22)</v>
-      </c>
-      <c r="G22" t="s">
-        <v>18</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -974,13 +948,10 @@
       <c r="D25" s="6">
         <v>5</v>
       </c>
-      <c r="E25" s="7">
-        <f>FV(C25,D25,,B25)</f>
-        <v>1722.7551914062499</v>
-      </c>
-      <c r="F25" t="str">
+      <c r="E25" s="7"/>
+      <c r="F25" t="e">
         <f ca="1">_xlfn.FORMULATEXT(E25)</f>
-        <v>=FV(C25,D25,,B25)</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">

--- a/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
+++ b/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Financial Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E6C36D-9E7E-4DBF-B204-9F75B7C77256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45270E2A-822A-4F07-BA9D-47B000FC07AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
   <si>
     <t>Prinicipal Amount</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>FV - Future Value</t>
+  </si>
+  <si>
+    <t>Nper - Time</t>
   </si>
 </sst>
 </file>
@@ -723,10 +726,16 @@
       <c r="D10" s="6">
         <v>5</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8" t="e">
+      <c r="E10" s="7">
+        <f>FV(C10,D10,,B10)</f>
+        <v>100010.55706850003</v>
+      </c>
+      <c r="F10" s="8" t="str">
         <f ca="1">_xlfn.FORMULATEXT(E10)</f>
-        <v>#N/A</v>
+        <v>=FV(C10,D10,,B10)</v>
+      </c>
+      <c r="G10" t="s">
+        <v>17</v>
       </c>
       <c r="H10" s="9"/>
       <c r="J10" s="10"/>
@@ -770,7 +779,7 @@
         <v>46</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>4</v>
@@ -793,10 +802,13 @@
       <c r="D13" s="6">
         <v>3</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" t="e">
+      <c r="E13" s="7">
+        <f>PMT(C13,D13,B13)</f>
+        <v>-25450.051153737099</v>
+      </c>
+      <c r="F13" t="str">
         <f ca="1">_xlfn.FORMULATEXT(E13)</f>
-        <v>#N/A</v>
+        <v>=PMT(C13,D13,B13)</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>

--- a/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
+++ b/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Financial Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45270E2A-822A-4F07-BA9D-47B000FC07AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB425DA-7F98-4848-A8DF-301CB3ABF845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
   </bookViews>
@@ -803,12 +803,12 @@
         <v>3</v>
       </c>
       <c r="E13" s="7">
-        <f>PMT(C13,D13,B13)</f>
-        <v>-25450.051153737099</v>
+        <f>PMT(C13/12,D13*12,B13)</f>
+        <v>-2051.8899325312309</v>
       </c>
       <c r="F13" t="str">
         <f ca="1">_xlfn.FORMULATEXT(E13)</f>
-        <v>=PMT(C13,D13,B13)</v>
+        <v>=PMT(C13/12,D13*12,B13)</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -846,10 +846,13 @@
       <c r="D16" s="6">
         <v>3</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" t="e">
+      <c r="E16" s="7">
+        <f>PPMT(C16/12,1,D16*12,B16)</f>
+        <v>-1591.4732658645644</v>
+      </c>
+      <c r="F16" t="str">
         <f ca="1">_xlfn.FORMULATEXT(E16)</f>
-        <v>#N/A</v>
+        <v>=PPMT(C16/12,1,D16*12,B16)</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">

--- a/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
+++ b/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Financial Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB425DA-7F98-4848-A8DF-301CB3ABF845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68200599-7C94-407B-B834-EDA03C9720F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
   </bookViews>
@@ -887,10 +887,13 @@
       <c r="D19" s="6">
         <v>3</v>
       </c>
-      <c r="E19" s="7"/>
-      <c r="F19" t="e">
+      <c r="E19" s="7">
+        <f>IPMT(C19/12,1,D19*12,B19)</f>
+        <v>-460.41666666666674</v>
+      </c>
+      <c r="F19" t="str">
         <f ca="1">_xlfn.FORMULATEXT(E19)</f>
-        <v>#N/A</v>
+        <v>=IPMT(C19/12,1,D19*12,B19)</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">

--- a/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
+++ b/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Financial Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68200599-7C94-407B-B834-EDA03C9720F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A5BD59-099E-4333-82E8-20D2185DAF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Prinicipal Amount</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>Nper - Time</t>
+  </si>
+  <si>
+    <t>per - Month</t>
   </si>
 </sst>
 </file>
@@ -790,6 +793,9 @@
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="G12" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="23"/>
@@ -928,10 +934,13 @@
       <c r="D22" s="6">
         <v>5</v>
       </c>
-      <c r="E22" s="7"/>
-      <c r="F22" t="e">
+      <c r="E22" s="7">
+        <f>FV(C22,D22,,B22)</f>
+        <v>37160.327581525875</v>
+      </c>
+      <c r="F22" t="str">
         <f ca="1">_xlfn.FORMULATEXT(E22)</f>
-        <v>#N/A</v>
+        <v>=FV(C22,D22,,B22)</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -966,10 +975,13 @@
       <c r="D25" s="6">
         <v>5</v>
       </c>
-      <c r="E25" s="7"/>
-      <c r="F25" t="e">
+      <c r="E25" s="7">
+        <f>FV(C25/12,D25*12,B25)</f>
+        <v>87032.52638908787</v>
+      </c>
+      <c r="F25" t="str">
         <f ca="1">_xlfn.FORMULATEXT(E25)</f>
-        <v>#N/A</v>
+        <v>=FV(C25/12,D25*12,B25)</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">

--- a/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
+++ b/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Financial Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A5BD59-099E-4333-82E8-20D2185DAF57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BA77DC-D9F8-45B5-B20A-2B9805E39080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
   </bookViews>
@@ -1016,10 +1016,13 @@
       <c r="D28" s="6">
         <v>80000</v>
       </c>
-      <c r="E28" s="16"/>
-      <c r="F28" t="e">
+      <c r="E28" s="16">
+        <f>RATE(C28*4,,B28,D28)</f>
+        <v>0.10496899164073202</v>
+      </c>
+      <c r="F28" t="str">
         <f ca="1">_xlfn.FORMULATEXT(E28)</f>
-        <v>#N/A</v>
+        <v>=RATE(C28*4,,B28,D28)</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1053,10 +1056,13 @@
       <c r="D31" s="5">
         <v>0.10496800000000001</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" t="e">
+      <c r="E31" s="7">
+        <f>PV(D31,B31*4,,C31)</f>
+        <v>-1476.0529856917199</v>
+      </c>
+      <c r="F31" t="str">
         <f ca="1">_xlfn.FORMULATEXT(E31)</f>
-        <v>#N/A</v>
+        <v>=PV(D31,B31*4,,C31)</v>
       </c>
       <c r="G31" s="10"/>
     </row>
@@ -1092,10 +1098,13 @@
       <c r="D34" s="6">
         <v>50000</v>
       </c>
-      <c r="E34" s="18"/>
-      <c r="F34" t="e">
+      <c r="E34" s="18">
+        <f>NPER(C34/12,B34,,D34)</f>
+        <v>30.008719519717197</v>
+      </c>
+      <c r="F34" t="str">
         <f ca="1">_xlfn.FORMULATEXT(E34)</f>
-        <v>#N/A</v>
+        <v>=NPER(C34/12,B34,,D34)</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
+++ b/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BA77DC-D9F8-45B5-B20A-2B9805E39080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
+++ b/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Financial Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BA77DC-D9F8-45B5-B20A-2B9805E39080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C401AA02-940B-4937-A31B-4CF623B93180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
   <si>
     <t>Prinicipal Amount</t>
   </si>
@@ -92,6 +92,34 @@
   </si>
   <si>
     <t>per - Month</t>
+  </si>
+  <si>
+    <t>What-if Analysis</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">there click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Goal Seek</t>
+    </r>
+  </si>
+  <si>
+    <t>then enter the required the set ce</t>
+  </si>
+  <si>
+    <t>what value needed to be changed that should be entered.</t>
+  </si>
+  <si>
+    <t>then which value needed to be changed.</t>
   </si>
 </sst>
 </file>
@@ -105,7 +133,7 @@
     <numFmt numFmtId="167" formatCode="&quot;£&quot;#,##0.00;[Red]\-&quot;£&quot;#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +151,14 @@
     <font>
       <b/>
       <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -266,7 +302,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -301,6 +337,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -671,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19061382-15BA-4790-91D1-B6A3F04B2D57}">
-  <dimension ref="A4:AD34"/>
+  <dimension ref="A3:AD34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.6328125" customWidth="1"/>
@@ -683,6 +720,11 @@
     <col min="10" max="10" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="J3" s="24" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
         <v>13</v>
@@ -692,6 +734,9 @@
       <c r="D4" s="21"/>
       <c r="E4" s="21"/>
       <c r="F4" s="21"/>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5" s="21"/>
@@ -700,6 +745,19 @@
       <c r="D5" s="21"/>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="8" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="9" spans="1:30" x14ac:dyDescent="0.35">

--- a/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
+++ b/Financial Functions/FINANCIAL FUNCTIONS QUESTIONS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Financial Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C401AA02-940B-4937-A31B-4CF623B93180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C57AC3-1B56-49A9-9E7D-8721ECD26CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{29C95F6E-244C-4ECB-89DA-68F6A5B818FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
   <si>
     <t>Prinicipal Amount</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>then which value needed to be changed.</t>
+  </si>
+  <si>
+    <t>will be used only if there is no restition and only one value needed to be changed.</t>
   </si>
 </sst>
 </file>
@@ -302,7 +305,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -338,6 +341,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -718,11 +724,16 @@
     <col min="6" max="6" width="25.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.7265625" customWidth="1"/>
+    <col min="16" max="16" width="19.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J3" s="24" t="s">
         <v>19</v>
+      </c>
+      <c r="P3" s="25" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.35">
@@ -737,6 +748,7 @@
       <c r="J4" t="s">
         <v>20</v>
       </c>
+      <c r="P4" s="25"/>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5" s="21"/>
@@ -748,16 +760,19 @@
       <c r="J5" t="s">
         <v>21</v>
       </c>
+      <c r="P5" s="25"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J6" t="s">
         <v>22</v>
       </c>
+      <c r="P6" s="25"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J7" t="s">
         <v>23</v>
       </c>
+      <c r="P7" s="25"/>
     </row>
     <row r="8" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="9" spans="1:30" x14ac:dyDescent="0.35">
@@ -1166,7 +1181,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="P3:P7"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="A4:F5"/>
